--- a/03-Relatorios/99-Avaliacao_IA/dados_avaliacao_ia.xlsx
+++ b/03-Relatorios/99-Avaliacao_IA/dados_avaliacao_ia.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C2" t="n">
         <v>100</v>
@@ -466,7 +466,7 @@
         <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="4">
@@ -479,7 +479,7 @@
         <v>29</v>
       </c>
       <c r="C4" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +492,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="6">
@@ -505,7 +505,7 @@
         <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="7">
@@ -518,7 +518,7 @@
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>16.7</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="9">
@@ -544,7 +544,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="10">
@@ -557,7 +557,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1827,7 +1827,6 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2202,10 +2201,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="n">
-        <v>70.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2228,7 +2227,7 @@
         <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="4">
@@ -2251,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2274,7 +2273,7 @@
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="6">
@@ -2297,7 +2296,7 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -2340,10 +2339,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" t="n">
-        <v>77.2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -2366,7 +2365,7 @@
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
@@ -2389,7 +2388,7 @@
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="11">
@@ -2435,7 +2434,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13">
@@ -2458,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -2478,10 +2477,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="15">
@@ -2504,7 +2503,7 @@
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="16">
@@ -2668,13 +2667,13 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="G2" t="n">
-        <v>10.5</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -2695,13 +2694,13 @@
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>9.6</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="4">
@@ -2722,13 +2721,13 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>7.9</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="5">
@@ -2749,13 +2748,13 @@
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>7.9</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="6">
@@ -2776,13 +2775,13 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>9.6</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="7">
@@ -2803,13 +2802,13 @@
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="8">
@@ -2830,13 +2829,13 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>7.9</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="9">
@@ -2857,13 +2856,13 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>8.800000000000001</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2884,13 +2883,13 @@
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="11">
@@ -2911,13 +2910,13 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
         <v>5.3</v>
       </c>
       <c r="G11" t="n">
-        <v>5.3</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="12">
@@ -2938,13 +2937,13 @@
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="13">
@@ -2965,13 +2964,13 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="14">
@@ -2992,13 +2991,13 @@
         <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="15">
@@ -3016,16 +3015,16 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E15" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F15" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="G15" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="16">
@@ -3040,19 +3039,19 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>104</v>
+      </c>
+      <c r="E16" t="n">
+        <v>113</v>
+      </c>
+      <c r="F16" t="n">
         <v>8</v>
       </c>
-      <c r="D16" t="n">
-        <v>106</v>
-      </c>
-      <c r="E16" t="n">
-        <v>114</v>
-      </c>
-      <c r="F16" t="n">
-        <v>7</v>
-      </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3070,10 +3069,10 @@
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E17" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F17" t="n">
         <v>8.800000000000001</v>
@@ -3103,7 +3102,7 @@
         <v>22</v>
       </c>
       <c r="F18" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
         <v>40.9</v>
@@ -3130,7 +3129,7 @@
         <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="G19" t="n">
         <v>36.4</v>
@@ -3157,7 +3156,7 @@
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="G20" t="n">
         <v>31.8</v>
@@ -3184,7 +3183,7 @@
         <v>22</v>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="G21" t="n">
         <v>36.4</v>
@@ -3319,7 +3318,7 @@
         <v>22</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="G26" t="n">
         <v>36.4</v>
@@ -3373,7 +3372,7 @@
         <v>22</v>
       </c>
       <c r="F28" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="G28" t="n">
         <v>54.5</v>
@@ -3400,7 +3399,7 @@
         <v>22</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="G29" t="n">
         <v>36.4</v>
@@ -3424,13 +3423,13 @@
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G30" t="n">
-        <v>2.6</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="31">
@@ -3451,13 +3450,13 @@
         <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
         <v>5.3</v>
       </c>
       <c r="G31" t="n">
-        <v>5.3</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="32">
@@ -3478,13 +3477,13 @@
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F32" t="n">
         <v>4.4</v>
       </c>
       <c r="G32" t="n">
-        <v>4.4</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="33">
@@ -3505,13 +3504,13 @@
         <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F33" t="n">
         <v>4.4</v>
       </c>
       <c r="G33" t="n">
-        <v>4.4</v>
+        <v>45.5</v>
       </c>
     </row>
   </sheetData>
@@ -3560,7 +3559,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3578,7 +3577,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3593,14 +3592,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GSI, IOERJ, JAPERI, MARICÁ, NITERÓI, QUEIMADOS, SEAP, SÃO PEDRO DA ALDEIA, UERJ</t>
+          <t>CEDAE, GSI, IOERJ, JAPERI, MARICÁ, NITERÓI, QUEIMADOS, SEAP, SÃO PEDRO DA ALDEIA, UERJ</t>
         </is>
       </c>
     </row>
@@ -3611,14 +3610,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GSI, IOERJ, JAPERI, MARICÁ, MPERJ, NITERÓI, PRODERJ, SEAP, SEPLAG, SÃO PEDRO DA ALDEIA, UERJ</t>
+          <t>CEDAE, GSI, IOERJ, JAPERI, MARICÁ, MPERJ, NITERÓI, PRODERJ, SEAP, SEPLAG, SÃO PEDRO DA ALDEIA, UERJ</t>
         </is>
       </c>
     </row>
@@ -3629,14 +3628,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MARICÁ, MESQUITA, NITERÓI, PRODERJ, QUEIMADOS</t>
+          <t>CEDAE, MARICÁ, MESQUITA, NITERÓI, PRODERJ, QUEIMADOS</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3667,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3686,7 +3685,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3704,7 +3703,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3722,7 +3721,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5439,7 +5438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6567,6 +6566,48 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CEDAE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>A soluções existentes -  Google Gemini (vinculado ao Google WorkSpace) e Microsoft Copilot - são utilizadas para suporte às atividades administrativas pelos funcionários da CEDAE.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8010,10 +8051,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>31.6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -8026,7 +8067,7 @@
         <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="4">
@@ -8039,7 +8080,7 @@
         <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="5">
@@ -8052,7 +8093,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="6">
@@ -8065,7 +8106,7 @@
         <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="7">
@@ -8078,7 +8119,7 @@
         <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="8">
@@ -8091,7 +8132,7 @@
         <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="9">
@@ -8104,7 +8145,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -8117,7 +8158,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="11">
@@ -8130,7 +8171,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="12">
@@ -8143,7 +8184,7 @@
         <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -8157,7 +8198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11161,7 +11202,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IASERJ</t>
+          <t>FTM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -11181,7 +11222,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>O Órgão não utiliza a Inteligência Artificial para nenhuma finalidade.</t>
+          <t>Ainda não utilizamos a Inteligencia Artificial na Fundação.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -11193,7 +11234,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FTM</t>
+          <t>SEDEC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -11213,7 +11254,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ainda não utilizamos a Inteligencia Artificial na Fundação.</t>
+          <t>A SEDEC não utiliza soluções de inteligência artificial de forma institucional em suas operações até a data de resposta deste questionário.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -11225,7 +11266,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SEDEC</t>
+          <t>CEPERJ</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -11245,19 +11286,19 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>A SEDEC não utiliza soluções de inteligência artificial de forma institucional em suas operações até a data de resposta deste questionário.</t>
+          <t>A Fundação CEPERJ ainda não iniciou ações para o uso de IA.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ausência de uso declarada ou não institucionalização</t>
+          <t>Uso descrito sem categoria específica</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CEPERJ</t>
+          <t>CEDAE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -11277,19 +11318,19 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>A Fundação CEPERJ ainda não iniciou ações para o uso de IA.</t>
+          <t>A soluções existentes -  Google Gemini (vinculado ao Google WorkSpace) e Microsoft Copilot - são utilizadas para suporte às atividades administrativas pelos funcionários da CEDAE.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Uso descrito sem categoria específica</t>
+          <t>Apoio textual, pesquisa e produtividade</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CEDAE</t>
+          <t>DERRJ</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -11307,21 +11348,16 @@
           <t>Não adota.</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>A soluções existentes -  Google Gemini (vinculado ao Google WorkSpace) e Microsoft Copilot - são utilizadas para suporte às atividades administrativas pelos funcionários da CEDAE.</t>
-        </is>
-      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Apoio textual, pesquisa e produtividade</t>
+          <t>Sem resposta aberta</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DERRJ</t>
+          <t>FSC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -11339,16 +11375,21 @@
           <t>Não adota.</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Esta Fundação Santa Cabrini não faz uso de Inteligência artificial</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sem resposta aberta</t>
+          <t>Uso descrito sem categoria específica</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FSC</t>
+          <t>UERJ</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -11367,38 +11408,6 @@
         </is>
       </c>
       <c r="E96" t="inlineStr">
-        <is>
-          <t>Esta Fundação Santa Cabrini não faz uso de Inteligência artificial</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Uso descrito sem categoria específica</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>UERJ</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
         <is>
           <t>A UERJ utiliza, em caráter experimental, a solução SollAI, ferramenta de inteligência artificial 
 generativa especializada em licitações, contratos e gestão pública. A solução tem por finalidade o apoio a processos licitatórios, 
@@ -11411,26 +11420,53 @@
 desenvolvidas internamente em uso oficial.</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Apoio textual, pesquisa e produtividade; Automação administrativa ou processual; Segurança, fraude ou fiscalização; Projeto-piloto, estudo ou prova de conceito; Contratação ou solução de terceiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>BARRA DO PIRAÍ</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Apoio textual, pesquisa e produtividade; Automação administrativa ou processual; Segurança, fraude ou fiscalização; Projeto-piloto, estudo ou prova de conceito; Contratação ou solução de terceiro</t>
+          <t>Sem resposta aberta</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BARRA DO PIRAÍ</t>
+          <t>MPERJ</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -11438,34 +11474,7 @@
           <t>Não adota.</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Sem resposta aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>MPERJ</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Adota em maior parte ou totalmente.</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>Resposta:
 Os principais usos de inteligência artificial atualmente existentes no MPRJ estão voltados ao apoio
@@ -11518,67 +11527,67 @@
 processamento assíncrono, OCR e validação automática de arquivos. Área Responsável: NIA - SGMTI</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Assistente virtual/chatbot/atendimento; Apoio textual, pesquisa e produtividade; Análise de dados, BI ou apoio à decisão; Automação administrativa ou processual; Desenvolvimento de software ou suporte técnico; Contratação ou solução de terceiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ANGRA DOS REIS</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Hoje, a principal aplicação prática de Inteligência Artificial dentro da organização está concentrada no apoio à gestão pública, elaboração documental, análise de processos e planejamento estratégico por meio do ChatGPT. Em paralelo, começam a surgir iniciativas institucionais mais estruturadas envolvendo IA, voltada para codificação de sistemas desenvolvidos pela área de TI
+O estágio atual do Município pode ser classificado como adoção inicial de IA para apoio à gestão e tomada de decisão, com potencial de evolução para aplicações operacionais voltadas ao cidadão e à automação de processos administrativos nos próximos ciclos de Transformação Digital.</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Assistente virtual/chatbot/atendimento; Apoio textual, pesquisa e produtividade; Análise de dados, BI ou apoio à decisão; Automação administrativa ou processual; Desenvolvimento de software ou suporte técnico; Contratação ou solução de terceiro</t>
+          <t>Apoio textual, pesquisa e produtividade; Análise de dados, BI ou apoio à decisão; Automação administrativa ou processual; Desenvolvimento de software ou suporte técnico; Projeto-piloto, estudo ou prova de conceito</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ANGRA DOS REIS</t>
+          <t>TCE-RJ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
-        <is>
-          <t>Hoje, a principal aplicação prática de Inteligência Artificial dentro da organização está concentrada no apoio à gestão pública, elaboração documental, análise de processos e planejamento estratégico por meio do ChatGPT. Em paralelo, começam a surgir iniciativas institucionais mais estruturadas envolvendo IA, voltada para codificação de sistemas desenvolvidos pela área de TI
-O estágio atual do Município pode ser classificado como adoção inicial de IA para apoio à gestão e tomada de decisão, com potencial de evolução para aplicações operacionais voltadas ao cidadão e à automação de processos administrativos nos próximos ciclos de Transformação Digital.</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Apoio textual, pesquisa e produtividade; Análise de dados, BI ou apoio à decisão; Automação administrativa ou processual; Desenvolvimento de software ou suporte técnico; Projeto-piloto, estudo ou prova de conceito</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>TCE-RJ</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Adota em maior parte ou totalmente.</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
         <is>
           <t>A organização estruturou o uso de inteligência artificial por meio de um plano estratégico institucional, com iniciativas que abrangem produtividade individual,
 apoio à atividade finalística e transformação digital dos processos.
@@ -11613,16 +11622,48 @@
 Estágio: contínuo</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Assistente virtual/chatbot/atendimento; Apoio textual, pesquisa e produtividade; Análise de dados, BI ou apoio à decisão; Automação administrativa ou processual; Segurança, fraude ou fiscalização; Desenvolvimento de software ou suporte técnico; Projeto-piloto, estudo ou prova de conceito; Contratação ou solução de terceiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SEDSDH</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Não é executado nenhum desenvolvimento interno ou há contratação de terceiros para o mesmo</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Assistente virtual/chatbot/atendimento; Apoio textual, pesquisa e produtividade; Análise de dados, BI ou apoio à decisão; Automação administrativa ou processual; Segurança, fraude ou fiscalização; Desenvolvimento de software ou suporte técnico; Projeto-piloto, estudo ou prova de conceito; Contratação ou solução de terceiro</t>
+          <t>Desenvolvimento de software ou suporte técnico; Contratação ou solução de terceiro</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SEDSDH</t>
+          <t>SECC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11642,19 +11683,19 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Não é executado nenhum desenvolvimento interno ou há contratação de terceiros para o mesmo</t>
+          <t>Não existe uso formal de IA na organização. Existe  uma demanda específica para contratar uma IA, que automatize um processo de geração de dados, para auxiliar na tomada de decisões. Esta iniciativa pertence a uma unidade de TI de área fim, destinada ao acompanhamento do PACTO-RJ. A COOTI auxiliaria na contratação da solução.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Desenvolvimento de software ou suporte técnico; Contratação ou solução de terceiro</t>
+          <t>Ausência de uso declarada ou não institucionalização; Automação administrativa ou processual; Contratação ou solução de terceiro</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SECC</t>
+          <t>DRM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11674,24 +11715,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Não existe uso formal de IA na organização. Existe  uma demanda específica para contratar uma IA, que automatize um processo de geração de dados, para auxiliar na tomada de decisões. Esta iniciativa pertence a uma unidade de TI de área fim, destinada ao acompanhamento do PACTO-RJ. A COOTI auxiliaria na contratação da solução.</t>
+          <t>NÃO ADOTA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ausência de uso declarada ou não institucionalização; Automação administrativa ou processual; Contratação ou solução de terceiro</t>
+          <t>Ausência de uso declarada ou não institucionalização</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DRM</t>
+          <t>MARICÁ</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -11705,38 +11746,6 @@
         </is>
       </c>
       <c r="E104" t="inlineStr">
-        <is>
-          <t>NÃO ADOTA</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Ausência de uso declarada ou não institucionalização</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>MARICÁ</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
         <is>
           <t>Justificativa apresentada pela Órgão Contratante:
 A presente contratação justifica-se pela necessidade da Administração Pública de Maricá em dispor de uma ferramenta digital que auxilie na automação de processos e na manipulação segura de dados sensíveis, a fim de garantir que as atividades administrativas sejam executadas com maior rapidez, precisão e segurança, em conformidade com os princípios da eficiência e economicidade previstos na Lei 14.133/2021.
@@ -11746,31 +11755,58 @@
 Sendo assim, conclui-se que a presente contratação é fundamental para Secretaria, além de ser tecnicamente viável e necessária a contratação, cujo investimento fortalecerá prontamente a capacidade e eficiência no cumprimento efetivo de suas ações e competências legais.</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Apoio textual, pesquisa e produtividade; Análise de dados, BI ou apoio à decisão; Automação administrativa ou processual; Segurança, fraude ou fiscalização; Projeto-piloto, estudo ou prova de conceito; Contratação ou solução de terceiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Apoio textual, pesquisa e produtividade; Análise de dados, BI ou apoio à decisão; Automação administrativa ou processual; Segurança, fraude ou fiscalização; Projeto-piloto, estudo ou prova de conceito; Contratação ou solução de terceiro</t>
+          <t>Sem resposta aberta</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SES</t>
+          <t>ITERJ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Adota em maior parte ou totalmente.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Adota em maior parte ou totalmente.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Adota parcialmente.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -11782,12 +11818,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ITERJ</t>
+          <t>CODIN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -11800,34 +11836,7 @@
           <t>Não adota.</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Sem resposta aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>CODIN</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>Ferramentas de apoio ao desenvolvimento e automação: utilização de soluções com IA pela área de TI para apoio à programação, automação de rotinas, desenvolvimento em Python e gerenciamento de ambientes Docker. Uso em estágio operacional e experimental, com ferramentas disponibilizadas por terceiros.
 Assistentes virtuais e chatbots de IA generativa: empregados por servidores para apoio na elaboração e revisão de textos,
@@ -11835,16 +11844,48 @@
 Ambientes de desenvolvimento assistido por IA: plataformas utilizadas para apoio à codificação, depuração, documentação técnica e maior agilidade no desenvolvimento de sistemas e scripts internos. Utilização restrita à área técnica de TI, com soluções contratadas ou disponibilizadas por terceiros.</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Assistente virtual/chatbot/atendimento; Apoio textual, pesquisa e produtividade; Análise de dados, BI ou apoio à decisão; Automação administrativa ou processual; Desenvolvimento de software ou suporte técnico; Contratação ou solução de terceiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PETRÓPOLIS</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Conforme respostas anteriores não fazemos uso de inteligência artificial organizadas por uma diretriz definidas em âmbito da Prefeitura. O que percebemos é o uso por alguns usuários no auxilio de determinadas tarefas, buscando para tanto sites em IA disponíveis na internet.</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Assistente virtual/chatbot/atendimento; Apoio textual, pesquisa e produtividade; Análise de dados, BI ou apoio à decisão; Automação administrativa ou processual; Desenvolvimento de software ou suporte técnico; Contratação ou solução de terceiro</t>
+          <t>Análise de dados, BI ou apoio à decisão</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PETRÓPOLIS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -11862,26 +11903,21 @@
           <t>Não adota.</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Conforme respostas anteriores não fazemos uso de inteligência artificial organizadas por uma diretriz definidas em âmbito da Prefeitura. O que percebemos é o uso por alguns usuários no auxilio de determinadas tarefas, buscando para tanto sites em IA disponíveis na internet.</t>
-        </is>
-      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Análise de dados, BI ou apoio à decisão</t>
+          <t>Sem resposta aberta</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SÃO GONÇALO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota em menor parte.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -11894,21 +11930,26 @@
           <t>Não adota.</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>No momento adquirimos Hardware e estamos em faze de teste para utilizaçao de LLM em nosso datacenter</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sem resposta aberta</t>
+          <t>Desenvolvimento de software ou suporte técnico; Projeto-piloto, estudo ou prova de conceito</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO</t>
+          <t>EMATER</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Adota em menor parte.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -11923,83 +11964,78 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>No momento adquirimos Hardware e estamos em faze de teste para utilizaçao de LLM em nosso datacenter</t>
+          <t>Não adota</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Desenvolvimento de software ou suporte técnico; Projeto-piloto, estudo ou prova de conceito</t>
+          <t>Ausência de uso declarada ou não institucionalização</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EMATER</t>
+          <t>PGE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Não adota</t>
+          <t>A PGE-RJ possui solução própria de inteligência artificial, desenvolvida por servidores da Gerência de Tecnologia da Informação para uso de toda à Procuradoria.  As soluções estão sustentadas em infraestrutura própria, com destaque para o projeto L.E.V.I., voltado à aplicação de Machine Learning na automação de tarefas repetitivas, especialmente em demandas de massa, na classificação de processos administrativos e judiciais, na predição de temas e teses e no apoio à proposição automatizada de respostas às demandas apresentadas. A partir dessa base institucional, a PGE-RJ/GTI desenvolveu internamente soluções, como o LEVI Chat, assistente jurídico conversacional integrado aos modelos L.E.V.I., voltado à pesquisa jurídica, análise de autos, geração de minutas, resumo de documentos e consulta a pareceres; a Consulta de Pareceres por IA, destinada à pesquisa inteligente no acervo de pareceres, com busca generativa, semântica e por filtros; o Raio-X, que realiza a extração automática de dados estruturados e informações-chave de demandas judiciais para triagem inicial; o Resumo de Documentos, voltado à síntese de sentenças, acórdãos e documentos jurídicos, com estruturação de metadados, fundamentos e dispositivo; e o Relatório do Processo, que consolida múltiplos documentos dos autos em visão cronológica e estruturada do caso. Há, ainda, iniciativas correlatas em diferentes estágios de uso ou consolidação, como classificação de êxito de sentenças, integração com o PGE Digital e análise de prestações de contas, todas desenvolvidas internamente e orientadas à redução de tarefas operacionais, ao aumento da qualidade da informação e à liberação de tempo técnico para a atuação jurídica estratégica.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ausência de uso declarada ou não institucionalização</t>
+          <t>Assistente virtual/chatbot/atendimento; Apoio textual, pesquisa e produtividade; Automação administrativa ou processual; Projeto-piloto, estudo ou prova de conceito</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PGE</t>
+          <t>ISP</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Adota em maior parte ou totalmente.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Adota em maior parte ou totalmente.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>A PGE-RJ possui solução própria de inteligência artificial, desenvolvida por servidores da Gerência de Tecnologia da Informação para uso de toda à Procuradoria.  As soluções estão sustentadas em infraestrutura própria, com destaque para o projeto L.E.V.I., voltado à aplicação de Machine Learning na automação de tarefas repetitivas, especialmente em demandas de massa, na classificação de processos administrativos e judiciais, na predição de temas e teses e no apoio à proposição automatizada de respostas às demandas apresentadas. A partir dessa base institucional, a PGE-RJ/GTI desenvolveu internamente soluções, como o LEVI Chat, assistente jurídico conversacional integrado aos modelos L.E.V.I., voltado à pesquisa jurídica, análise de autos, geração de minutas, resumo de documentos e consulta a pareceres; a Consulta de Pareceres por IA, destinada à pesquisa inteligente no acervo de pareceres, com busca generativa, semântica e por filtros; o Raio-X, que realiza a extração automática de dados estruturados e informações-chave de demandas judiciais para triagem inicial; o Resumo de Documentos, voltado à síntese de sentenças, acórdãos e documentos jurídicos, com estruturação de metadados, fundamentos e dispositivo; e o Relatório do Processo, que consolida múltiplos documentos dos autos em visão cronológica e estruturada do caso. Há, ainda, iniciativas correlatas em diferentes estágios de uso ou consolidação, como classificação de êxito de sentenças, integração com o PGE Digital e análise de prestações de contas, todas desenvolvidas internamente e orientadas à redução de tarefas operacionais, ao aumento da qualidade da informação e à liberação de tempo técnico para a atuação jurídica estratégica.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Assistente virtual/chatbot/atendimento; Apoio textual, pesquisa e produtividade; Automação administrativa ou processual; Projeto-piloto, estudo ou prova de conceito</t>
+          <t>Sem resposta aberta</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ISP</t>
+          <t>CAMPOS DOS GOYTACAZES</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12017,39 +12053,12 @@
           <t>Não adota.</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>não adota</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
-        <is>
-          <t>Sem resposta aberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>CAMPOS DOS GOYTACAZES</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>não adota</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
         <is>
           <t>Ausência de uso declarada ou não institucionalização</t>
         </is>

--- a/03-Relatorios/99-Avaliacao_IA/dados_avaliacao_ia.xlsx
+++ b/03-Relatorios/99-Avaliacao_IA/dados_avaliacao_ia.xlsx
@@ -16,10 +16,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="auditados_diretrizes_controles" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="categorias_q3006_resumo" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="categorias_q3006_detalhe" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ajustes_pos_evidencia_ia" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="historico_ia_nao_aplicado" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sinais_maturidade_ia" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="controle_rastreabilidade" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="riscos_uso_contratacao_ia" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grupo_uso_contratacao_ia" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'historico_ia_nao_aplicado'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'controle_rastreabilidade'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'riscos_uso_contratacao_ia'!$A$1:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'grupo_uso_contratacao_ia'!$A$1:$G$36</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -27,13 +35,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -56,8 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,10 +480,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n">
-        <v>28.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="4">
@@ -476,10 +493,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>25.7</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="5">
@@ -489,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +545,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>17.7</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="9">
@@ -576,14 +593,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ajustes pós-evidência em questões de IA</t>
+          <t>Ajustes de IA aplicados na base final</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -597,8 +614,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -646,6 +669,26 @@
           <t>Justificativa do auditor revisor</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Aplicado na base final</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Apresentado no preliminar encaminhado</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Páginas do preliminar encaminhado</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Apresentado no relatório final</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -685,6 +728,26 @@
           <t>A Equipe de Auditoria avalia que a documentação apresentada é insuficiente para demonstrar um processo de identificação e avaliação contínua de novas oportunidades de aplicação de inteligência artificial. Embora a norma estabeleça diretrizes para a ferramenta já adotada, não foram apresentados registros, metodologias ou fluxos de trabalho destinados à prospecção, análise ou priorização de novas demandas institucionais. Identifica-se a lacuna na ausência de mecanismos estruturados que evidenciem a busca ativa por soluções tecnológicas alinhadas às necessidades estratégicas.</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -724,6 +787,26 @@
           <t>A norma técnica apresentada estabelece o bloqueio de ferramentas não autorizadas na rede, contudo, não comprova a existência de um processo para a identificação das ferramentas específicas que estão sendo acessadas. A evidência documental restringe-se à definição da política, sem apresentar registros, logs ou relatórios que permitam verificar a efetiva identificação das tentativas de acesso ou ferramentas públicas utilizadas na rede corporativa. A evidência é insuficiente pela ausência de relatórios de monitoramento de tráfego ou inventário de ferramentas detectadas.</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -763,6 +846,26 @@
           <t>A evidência apresentada consiste unicamente em um normativo institucional, a "Política de Inteligência Artificial", que estabelece diretrizes e governança para a tecnologia. Não foram fornecidos registros, contratos, inventários de sistemas ou relatórios que comprovem a utilização efetiva de inteligência artificial nas operações da organização.</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -801,6 +904,26 @@
           <t>O documento normativo define a responsabilidade das unidades em identificar oportunidades, conforme o Art. 12. Contudo, não foram apresentadas evidências documentais, como atas de reunião, relatórios de análise ou planejamentos estratégicos, que demonstrem a execução contínua desse processo.</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -839,6 +962,26 @@
           <t>Embora o normativo institua um Sandbox de Inovação para avaliações experimentais (Art. 17), não há comprovação da execução de projetos-piloto ou provas de conceito. A documentação apresentada não inclui planos de testes, escopos ou relatórios conclusivos de casos reais.</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -877,6 +1020,26 @@
           <t>A política menciona requisitos técnicos para o desenvolvimento de soluções, conforme Art. 13. Entretanto, não foram apresentadas evidências concretas de soluções desenvolvidas internamente, tais como documentação técnica, repositórios de código ou projetos específicos.</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -915,6 +1078,26 @@
           <t>A evidência restringe-se a normas regulatórias e não identifica sistemas operacionais em ambiente de produção. Não foi demonstrada a existência de nenhuma ferramenta de inteligência artificial em uso corrente apoiando processos internos da organização.</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -951,6 +1134,26 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>Não foram fornecidas evidências de soluções operacionais voltadas para atividades finalísticas ou serviços ao cidadão. O documento limita-se a disciplinar o uso, sem apresentar casos práticos de aplicação finalística.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -992,6 +1195,26 @@
           <t>A evidência apresentada é insuficiente para comprovar a contratação de serviço especializado em inteligência artificial. O Acordo de Cooperação Técnica (Processo SEI-320001/002554/2024, p. 1) trata exclusivamente de cessão não onerosa de solução tecnológica, conforme Cláusulas Primeira e Sétima. A Ordem de Serviço nº 34 (Processo SEI-320001/000406/2024, p. 2) descreve apenas serviços genéricos de TI, como manutenção, suporte e consultoria, sem qualquer vinculação explícita ou técnica a atividades relacionadas à inteligência artificial. Falta a apresentação de contrato, edital ou documento correlato que identifique expressamente a aquisição ou contratação de serviços de consultoria, desenvolvimento, treinamento ou sustentação voltados especificamente à inteligência artificial.</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1031,6 +1254,26 @@
           <t>A evidência documental comprova a contratação de uma suíte de colaboração e produtividade (Google Workspace) com serviços de migração, treinamento e customização, mas não contempla a contratação de inteligência artificial generativa. Os documentos contratuais, incluindo o termo aditivo e o termo de apostilamento, descrevem estritamente ferramentas de e-mail, drive, chat e videoconferência. Não foram identificados elementos, cláusulas ou especificações técnicas que fundamentem a aquisição ou utilização de soluções de IA generativa como objeto da contratação.</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1070,6 +1313,26 @@
           <t>Não há evidências documentais ou registros que comprovem a realização de etapas de projetos-piloto ou provas de conceito para as soluções apresentadas. A evidência restringiu-se a demonstrar o estágio de produção das ferramentas. Falta a apresentação de documentos de planejamento, relatórios de testes ou termos de início de projeto que caracterizem a experimentação.</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1109,6 +1372,26 @@
           <t>As imagens fornecidas atestam o uso das ferramentas, mas não contêm elementos que comprovem que o desenvolvimento ocorreu internamente. É necessária a apresentação de documentação técnica, registros de repositórios ou contratos que evidenciem a autoria ou o desenvolvimento pela própria equipe da instituição. Sem esses registros, não é possível confirmar o desenvolvimento interno.</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1148,6 +1431,26 @@
           <t>Embora a evidência mostre o sistema MinutaIA, não há descrição ou documentação que confirme sua aplicação estrita em processos administrativos internos. As imagens apresentam o sistema de forma genérica em ambiente institucional sem detalhar os fluxos de trabalho suportados. Faltam evidências adicionais que vinculem a ferramenta aos processos administrativos específicos da organização.</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1187,6 +1490,26 @@
           <t>Não foram apresentadas evidências documentais como atos normativos, portarias ou organogramas que comprovem a existência de uma estrutura formal de governança ou a designação de responsáveis por iniciativas de inteligência artificial. A ausência de um documento de designação formal impede a conformidade deste item.</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1225,8 +1548,29 @@
           <t>A evidência apresentada é considerada não conforme, visto que consiste integralmente em material publicitário público e não comprova a contratação efetiva dos serviços pela organização. O documento carece de elementos probatórios essenciais, tais como contrato, nota fiscal, empenho ou registro administrativo que vincule a entidade ao provedor do serviço. A análise técnica indica que o material possui natureza genérica e informativa, sem identificar a organização auditada como parte contratante ou usuária. Identifica-se como lacuna a ausência de qualquer documento formal ou ato administrativo que comprove a existência de vínculo contratual ou aquisição de licenças.</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1237,7 +1581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,7 +1744,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1427,69 +1771,69 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JUCERJA</t>
+          <t>CGE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Adota em maior parte ou totalmente.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Adota em maior parte ou totalmente.</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1497,91 +1841,91 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>O recurso de Inteligência Artificial é utilizado pela área finalística com p intuito de agilizar o procedimento de análise de julgamento  do processo de registro mercantil. O Setor responsável pelo projeto é a Secretaria Geral e a unidade usuário é a Superintendência de Registro e Comércio.</t>
+          <t>A organização faz uso da IA ANIA que ajuda nos processos SEI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PGE</t>
+          <t>JUCERJA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1604,97 +1948,189 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>A PGE-RJ possui solução própria de inteligência artificial, desenvolvida por servidores da Gerência de Tecnologia da Informação para uso de toda à Procuradoria.  As soluções estão sustentadas em infraestrutura própria, com destaque para o projeto L.E.V.I., voltado à aplicação de Machine Learning na automação de tarefas repetitivas, especialmente em demandas de massa, na classificação de processos administrativos e judiciais, na predição de temas e teses e no apoio à proposição automatizada de respostas às demandas apresentadas. A partir dessa base institucional, a PGE-RJ/GTI desenvolveu internamente soluções, como o LEVI Chat, assistente jurídico conversacional integrado aos modelos L.E.V.I., voltado à pesquisa jurídica, análise de autos, geração de minutas, resumo de documentos e consulta a pareceres; a Consulta de Pareceres por IA, destinada à pesquisa inteligente no acervo de pareceres, com busca generativa, semântica e por filtros; o Raio-X, que realiza a extração automática de dados estruturados e informações-chave de demandas judiciais para triagem inicial; o Resumo de Documentos, voltado à síntese de sentenças, acórdãos e documentos jurídicos, com estruturação de metadados, fundamentos e dispositivo; e o Relatório do Processo, que consolida múltiplos documentos dos autos em visão cronológica e estruturada do caso. Há, ainda, iniciativas correlatas em diferentes estágios de uso ou consolidação, como classificação de êxito de sentenças, integração com o PGE Digital e análise de prestações de contas, todas desenvolvidas internamente e orientadas à redução de tarefas operacionais, ao aumento da qualidade da informação e à liberação de tempo técnico para a atuação jurídica estratégica.</t>
+          <t>O recurso de Inteligência Artificial é utilizado pela área finalística com p intuito de agilizar o procedimento de análise de julgamento  do processo de registro mercantil. O Setor responsável pelo projeto é a Secretaria Geral e a unidade usuário é a Superintendência de Registro e Comércio.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>PGE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>A PGE-RJ possui solução própria de inteligência artificial, desenvolvida por servidores da Gerência de Tecnologia da Informação para uso de toda à Procuradoria.  As soluções estão sustentadas em infraestrutura própria, com destaque para o projeto L.E.V.I., voltado à aplicação de Machine Learning na automação de tarefas repetitivas, especialmente em demandas de massa, na classificação de processos administrativos e judiciais, na predição de temas e teses e no apoio à proposição automatizada de respostas às demandas apresentadas. A partir dessa base institucional, a PGE-RJ/GTI desenvolveu internamente soluções, como o LEVI Chat, assistente jurídico conversacional integrado aos modelos L.E.V.I., voltado à pesquisa jurídica, análise de autos, geração de minutas, resumo de documentos e consulta a pareceres; a Consulta de Pareceres por IA, destinada à pesquisa inteligente no acervo de pareceres, com busca generativa, semântica e por filtros; o Raio-X, que realiza a extração automática de dados estruturados e informações-chave de demandas judiciais para triagem inicial; o Resumo de Documentos, voltado à síntese de sentenças, acórdãos e documentos jurídicos, com estruturação de metadados, fundamentos e dispositivo; e o Relatório do Processo, que consolida múltiplos documentos dos autos em visão cronológica e estruturada do caso. Há, ainda, iniciativas correlatas em diferentes estágios de uso ou consolidação, como classificação de êxito de sentenças, integração com o PGE Digital e análise de prestações de contas, todas desenvolvidas internamente e orientadas à redução de tarefas operacionais, ao aumento da qualidade da informação e à liberação de tempo técnico para a atuação jurídica estratégica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>SEFAZ</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>A Secretaria de Estado de Fazenda do Rio de Janeiro (SEFAZ-RJ) implementou, em seus portais 
 de serviços tributários, uma solução de atendimento digital baseada em chatbot com o objetivo de 
@@ -1741,159 +2177,72 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Adota em maior parte ou totalmente.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Adota em maior parte ou totalmente.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SETD</t>
+          <t>SES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Adota em maior parte ou totalmente.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1912,101 +2261,188 @@
       <c r="Q7" t="inlineStr">
         <is>
           <t>Sim</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>A SUBEDD/SETD está desenvolvendo duas aplicações de assistente virtual que utilizam IA (tipo LLM, código aberto) para facilitar a experiência do usuário no portal RJ Digital e no sistema Radar RJ. A aplicação é desenvolvida internamente, por servidores públicos, utilizando-se a Plataforma contratada e disponibilizada pelo PRODERJ (Plataforma IBM Watson) para hospedagem e apoio ao desenvolvimento.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>SETD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>A SUBEDD/SETD está desenvolvendo duas aplicações de assistente virtual que utilizam IA (tipo LLM, código aberto) para facilitar a experiência do usuário no portal RJ Digital e no sistema Radar RJ. A aplicação é desenvolvida internamente, por servidores públicos, utilizando-se a Plataforma contratada e disponibilizada pelo PRODERJ (Plataforma IBM Watson) para hospedagem e apoio ao desenvolvimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TCE-RJ</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>A organização estruturou o uso de inteligência artificial por meio de um plano estratégico institucional, com iniciativas que abrangem produtividade individual,
 apoio à atividade finalística e transformação digital dos processos.
@@ -2042,93 +2478,93 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>TJRJ</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>ASSIS	Assistente para construção de minutas e responde perguntas sobre o processo.	ASSIA-SGTEC	Produção	Interno	Contratação Fábrica de Software de IA (SPASSU)
 JurisFlow	Extrator de dados estruturados de um documento jurídico.	ASSIA-SGTEC	Homologação	Interno	Contratação Fábrica de Software de IA (SPASSU)
@@ -2144,6 +2580,2113 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="86" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Verificação</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Data de referência das respostas</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Base final do questionário</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Data da revisão</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Conferência das bases e relatórios individuais</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Organizações comparadas</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Bases inicial, pós-evidências e final</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Campos de IA comparados</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Campos de respostas e evidências com prefixo q30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Células de IA comparadas em cada base</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>6328</v>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>113 organizações × 56 campos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Ajustes de IA aplicados após evidências</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Comparação dos valores da base inicial e da base pós-evidências</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Ajustes de IA aplicados após comentários</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Comparação dos valores da base pós-evidências e da base final</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Registros de IA nas planilhas vigentes de ajustes</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Planilhas de ajustes pós-evidências e pós-comentários</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ajustes de IA apresentados nos preliminares</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>PDFs encaminhados nos TSID03 de AGERIO, CGE, DPGE e CEDAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Ajustes de IA apresentados nos relatórios finais</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>113 relatórios individuais finais disponíveis</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Natureza dos resultados deste diagnóstico</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Autodeclarações</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Valores de IA preservados na base final</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Registros históricos preservados</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>15 registros com seus pareceres originais, sem aplicação na base vigente</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Aba historico_ia_nao_aplicado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Limite da interpretação</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>A preservação das respostas não comprova o acolhimento técnico das manifestações sobre IA</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Ausência de itens de IA nos produtos atuais de avaliação de comentários</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Categorias da questão aberta</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Uma resposta pode integrar mais de uma categoria. Percentuais calculados sobre 113 organizações</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Abas categorias_q3006_resumo e categorias_q3006_detalhe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SHA-256 da base</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>d8d048ae36813ac156ee51ebe6b5c1a684f8b2a1573db6d68e3f0516eff5d664</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>02-Execucao/01-Questionario/03-Respostas_Processadas/20260621-respostas-questionario-01-pos-ajuste-inicial.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SHA-256 da base</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>4ba5119d4560ca4a2268eb2ce16e94673c9414b8be2b6ee8c05abd502f7589cf</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>02-Execucao/01-Questionario/03-Respostas_Processadas/20260621-respostas-questionario-02-pos-avaliacao-evidencias.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>SHA-256 da base</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>13646413e7a78a89713937e5a5f01cffdff53e2d8b6972f7b9d67a74d1ee0e60</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>02-Execucao/01-Questionario/03-Respostas_Processadas/20260716-respostas-questionario-pos-comentarios-gestor.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Grupo para análise de riscos de IA</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>35</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3001 em um dos três níveis de adoção OU pelo menos um Sim em q3003[A], q3003[B] ou q3003[C]. Não inclui somente decisão ou plano de uso. Não utiliza a categorização interpretativa da q3006 para redefinir o grupo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ausência de adoção no grupo de uso/contratação</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Diretrizes: 21 (60,0%). Controles: 22 (62,9%).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Decisão ou plano aprovado não é contado como adoção nos dois indicadores de ausência de adoção.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="75" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="100" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Risco indicativo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Quantidade geral</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Percentual de 113</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Auditados geral</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Quantidade uso/contratação</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Percentual de 35</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Auditados uso/contratação</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Uso ou contratação de IA sem adoção de diretrizes</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ARRAIAL DO CABO, CEDAE, CODIN, DETRAN, DPGE, GSI, IOERJ, JAPERI, MARICÁ, MESQUITA, NITERÓI, QUEIMADOS, RIO DAS OSTRAS, SEAP, SECTI, SEPLAG, SETRAB, SÃO GONÇALO, SÃO PEDRO DA ALDEIA, TERESÓPOLIS, UERJ</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ARRAIAL DO CABO, CEDAE, CODIN, DETRAN, DPGE, GSI, IOERJ, JAPERI, MARICÁ, MESQUITA, NITERÓI, QUEIMADOS, RIO DAS OSTRAS, SEAP, SECTI, SEPLAG, SETRAB, SÃO GONÇALO, SÃO PEDRO DA ALDEIA, TERESÓPOLIS, UERJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Uso ou contratação de IA sem adoção de controles de IA generativa</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ARRAIAL DO CABO, CEDAE, CODIN, DETRAN, DPGE, FMIS, GSI, IOERJ, JAPERI, MARICÁ, MPERJ, NITERÓI, PRODERJ, QUEIMADOS, RIO DAS OSTRAS, SEAP, SEPLAG, SETRAB, SÃO GONÇALO, SÃO PEDRO DA ALDEIA, TERESÓPOLIS, UERJ</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ARRAIAL DO CABO, CEDAE, CODIN, DETRAN, DPGE, FMIS, GSI, IOERJ, JAPERI, MARICÁ, MPERJ, NITERÓI, PRODERJ, QUEIMADOS, RIO DAS OSTRAS, SEAP, SEPLAG, SETRAB, SÃO GONÇALO, SÃO PEDRO DA ALDEIA, TERESÓPOLIS, UERJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Medidas de IA generativa sem identificação de acessos na rede</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AGENERSA, CGE, DPGE, FLXIII, IPEM, JUCERJA, MESQUITA, PGE, QUEIMADOS, SEAPPA, SECEC, SECID, SEDEICS, SES, SETD, TCE-RJ, TERESÓPOLIS, TJRJ</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CGE, DPGE, IPEM, JUCERJA, MESQUITA, PGE, QUEIMADOS, SECID, SES, SETD, TCE-RJ, TERESÓPOLIS, TJRJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Diretrizes sem avaliação prévia de riscos</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AGENERSA, AGERIO, CGE, DPGE, FMIS, IPEM, IRM, MESQUITA, MPERJ, PGE, PRODERJ, SECID, SECTI, SEDEICS, SEPLAG, TERESÓPOLIS, UENF</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AGERIO, CGE, DPGE, FMIS, IPEM, MESQUITA, MPERJ, PGE, PRODERJ, SECID, SECTI, SEPLAG, TERESÓPOLIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Diretrizes sem revisão humana prevista</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AGENERSA, AGERIO, CGE, DPGE, IPEM, IRM, MESQUITA, PRODERJ, SECID, SECTI, SEDEICS, SEPLAG, SES, TCE-RJ, TERESÓPOLIS, UENF</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AGERIO, CGE, DPGE, IPEM, MESQUITA, PRODERJ, SECID, SECTI, SEPLAG, SES, TCE-RJ, TERESÓPOLIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Uso ou plano de IA sem controle de IA generativa</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ARRAIAL DO CABO, CABO FRIO, CODIN, DETRAN, FMIS, MARICÁ, MPERJ, NITERÓI, PRODERJ, RIO DAS OSTRAS, SEAP, SEPLAG, SETRAB, SÃO GONÇALO, SÃO PEDRO DA ALDEIA</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ARRAIAL DO CABO, CODIN, DETRAN, FMIS, MARICÁ, MPERJ, NITERÓI, PRODERJ, RIO DAS OSTRAS, SEAP, SEPLAG, SETRAB, SÃO GONÇALO, SÃO PEDRO DA ALDEIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Diretrizes sem regra para dados em prompts</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AGENERSA, DPGE, FMIS, IPEM, IRM, MESQUITA, PRODERJ, SECID, SECTI, SEDEICS, SEPLAG, TERESÓPOLIS, UENF</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DPGE, FMIS, IPEM, MESQUITA, PRODERJ, SECID, SECTI, SEPLAG, TERESÓPOLIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Uso ou plano de IA sem diretrizes formais</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ARRAIAL DO CABO, CABO FRIO, CODIN, DETRAN, MARICÁ, NITERÓI, QUEIMADOS, RIO DAS OSTRAS, SEAP, SETRAB, SÃO GONÇALO, SÃO PEDRO DA ALDEIA</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARRAIAL DO CABO, CODIN, DETRAN, MARICÁ, NITERÓI, QUEIMADOS, RIO DAS OSTRAS, SEAP, SETRAB, SÃO GONÇALO, SÃO PEDRO DA ALDEIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Contratação de IA sem controle de IA generativa</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CEDAE, GSI, IOERJ, JAPERI, MARICÁ, MPERJ, NITERÓI, PRODERJ, SEAP, SEPLAG, SÃO PEDRO DA ALDEIA, UERJ</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CEDAE, GSI, IOERJ, JAPERI, MARICÁ, MPERJ, NITERÓI, PRODERJ, SEAP, SEPLAG, SÃO PEDRO DA ALDEIA, UERJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Contratação de IA sem diretrizes formais</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CEDAE, GSI, IOERJ, JAPERI, MARICÁ, NITERÓI, QUEIMADOS, SEAP, SÃO PEDRO DA ALDEIA, UERJ</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CEDAE, GSI, IOERJ, JAPERI, MARICÁ, NITERÓI, QUEIMADOS, SEAP, SÃO PEDRO DA ALDEIA, UERJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IA generativa contratada sem diretrizes robustas</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CEDAE, DPGE, MARICÁ, MESQUITA, NITERÓI, PRODERJ, QUEIMADOS</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CEDAE, DPGE, MARICÁ, MESQUITA, NITERÓI, PRODERJ, QUEIMADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IA em produção sem diretrizes robustas</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DPGE, MARICÁ, NITERÓI, QUEIMADOS, SECTI</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DPGE, MARICÁ, NITERÓI, QUEIMADOS, SECTI</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>firstname</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>q3001</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>q3003[A]</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>q3003[B]</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>q3003[C]</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>q3002</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>q3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AGERIO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ARRAIAL DO CABO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CEDAE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CGE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CODIN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DETRAN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DPGE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FMIS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GSI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IOERJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IPEM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>JAPERI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>JUCERJA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MARICÁ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MESQUITA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NITERÓI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PGE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PRODERJ</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QUEIMADOS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RIO DAS OSTRAS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SEAP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SECTI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SEFAZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SEPLAG</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SETD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SETRAB</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SÃO GONÇALO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SÃO PEDRO DA ALDEIA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TCE-RJ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TERESÓPOLIS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TJRJ</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>UERJ</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2201,10 +4744,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" t="n">
-        <v>69.90000000000001</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -2270,10 +4813,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6">
@@ -2661,19 +5204,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>10.6</v>
+        <v>12.4</v>
       </c>
       <c r="G2" t="n">
-        <v>70.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2688,19 +5231,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>9.699999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="G3" t="n">
-        <v>64.7</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="4">
@@ -2715,19 +5258,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>52.9</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="5">
@@ -2742,19 +5285,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>52.9</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="6">
@@ -2769,19 +5312,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>9.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="G6" t="n">
-        <v>64.7</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2796,19 +5339,19 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="n">
         <v>8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>17</v>
       </c>
       <c r="F7" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>47.1</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="8">
@@ -3039,19 +5582,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E16" t="n">
         <v>113</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3066,19 +5609,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E17" t="n">
         <v>113</v>
       </c>
       <c r="F17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -3417,19 +5960,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
         <v>11</v>
       </c>
       <c r="F30" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="G30" t="n">
-        <v>27.3</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="31">
@@ -3628,14 +6171,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CEDAE, MARICÁ, MESQUITA, NITERÓI, PRODERJ, QUEIMADOS</t>
+          <t>CEDAE, DPGE, MARICÁ, MESQUITA, NITERÓI, PRODERJ, QUEIMADOS</t>
         </is>
       </c>
     </row>
@@ -3718,14 +6261,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8</v>
+        <v>15.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AGENERSA, AGERIO, CGE, DPGE, FLXIII, IPEM, JUCERJA, MESQUITA, PGE, QUEIMADOS, SEAPPA, SECEC, SECID, SEDEICS, SES, SETD, TCE-RJ, TERESÓPOLIS, TJRJ</t>
+          <t>AGENERSA, CGE, DPGE, FLXIII, IPEM, JUCERJA, MESQUITA, PGE, QUEIMADOS, SEAPPA, SECEC, SECID, SEDEICS, SES, SETD, TCE-RJ, TERESÓPOLIS, TJRJ</t>
         </is>
       </c>
     </row>
@@ -3740,7 +6283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3956,40 +6499,82 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>CGE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>A organização faz uso da IA ANIA que ajuda nos processos SEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>CODIN</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Ferramentas de apoio ao desenvolvimento e automação: utilização de soluções com IA pela área de TI para apoio à programação, automação de rotinas, desenvolvimento em Python e gerenciamento de ambientes Docker. Uso em estágio operacional e experimental, com ferramentas disponibilizadas por terceiros.
 Assistentes virtuais e chatbots de IA generativa: empregados por servidores para apoio na elaboração e revisão de textos,
@@ -3998,62 +6583,20 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DETRAN</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Adota em menor parte.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Existem projetos em desenvolvimento, ainda não finalizados.</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DPGE</t>
+          <t>DETRAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adota parcialmente.</t>
+          <t>Adota em menor parte.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4073,29 +6616,29 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Interações básicas para elucidação de temas técnicos das áreas de negócio; automações simples para facilitação de fluxos de trabalho.</t>
+          <t>Existem projetos em desenvolvimento, ainda não finalizados.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FMIS</t>
+          <t>DPGE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adota em menor parte.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Adota em maior parte ou totalmente.</t>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4105,7 +6648,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4115,19 +6658,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>A IA ORION NOVA É ATUALMENTE UTILIZADA COMO MECANISMO DE PESQUISA NAS EXPOSIÇÕES DO MIS LAPA. A SOLUÇÃO FOI DISPONIBILIZADA POR TERCEIRO.</t>
+          <t>Interações básicas para elucidação de temas técnicos das áreas de negócio; automações simples para facilitação de fluxos de trabalho.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IPEM</t>
+          <t>FMIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4137,7 +6680,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Adota em menor parte.</t>
+          <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4157,34 +6700,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Adota em menor parte.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não temos contratada.</t>
+          <t>A IA ORION NOVA É ATUALMENTE UTILIZADA COMO MECANISMO DE PESQUISA NAS EXPOSIÇÕES DO MIS LAPA. A SOLUÇÃO FOI DISPONIBILIZADA POR TERCEIRO.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JUCERJA</t>
+          <t>IPEM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adota parcialmente.</t>
+          <t>Adota em menor parte.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Adota em maior parte ou totalmente.</t>
+          <t>Adota em menor parte.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4194,57 +6737,99 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Adota em maior parte ou totalmente.</t>
+          <t>Adota em menor parte.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>O recurso de Inteligência Artificial é utilizado pela área finalística com p intuito de agilizar o procedimento de análise de julgamento  do processo de registro mercantil. O Setor responsável pelo projeto é a Secretaria Geral e a unidade usuário é a Superintendência de Registro e Comércio.</t>
+          <t>Não temos contratada.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>JUCERJA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O recurso de Inteligência Artificial é utilizado pela área finalística com p intuito de agilizar o procedimento de análise de julgamento  do processo de registro mercantil. O Setor responsável pelo projeto é a Secretaria Geral e a unidade usuário é a Superintendência de Registro e Comércio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>MARICÁ</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Justificativa apresentada pela Órgão Contratante:
 A presente contratação justifica-se pela necessidade da Administração Pública de Maricá em dispor de uma ferramenta digital que auxilie na automação de processos e na manipulação segura de dados sensíveis, a fim de garantir que as atividades administrativas sejam executadas com maior rapidez, precisão e segurança, em conformidade com os princípios da eficiência e economicidade previstos na Lei 14.133/2021.
@@ -4255,86 +6840,86 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>MESQUITA</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>A principal utilização de inteligência artificial é no Centro de Controle Operacional (CCO). Uma das funções da IA é na identificação de placas dos veículos identificados pelas câmeras.
 https://tecnologia.mesquita.rj.gov.br/?p=194</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>MPERJ</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Resposta:
 Os principais usos de inteligência artificial atualmente existentes no MPRJ estão voltados ao apoio
@@ -4388,43 +6973,43 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>NITERÓI</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>3006. Principais Usos de Inteligência Artificial na Organização
 Descreva os principais usos de inteligência artificial existentes na organização, indicando, quando possível, a finalidade, a área responsável, o estágio de utilização e se a solução é desenvolvida internamente, contratada ou disponibilizada por terceiro.
@@ -4529,85 +7114,85 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PGE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Adota em maior parte ou totalmente.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Adota em maior parte ou totalmente.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>A PGE-RJ possui solução própria de inteligência artificial, desenvolvida por servidores da Gerência de Tecnologia da Informação para uso de toda à Procuradoria.  As soluções estão sustentadas em infraestrutura própria, com destaque para o projeto L.E.V.I., voltado à aplicação de Machine Learning na automação de tarefas repetitivas, especialmente em demandas de massa, na classificação de processos administrativos e judiciais, na predição de temas e teses e no apoio à proposição automatizada de respostas às demandas apresentadas. A partir dessa base institucional, a PGE-RJ/GTI desenvolveu internamente soluções, como o LEVI Chat, assistente jurídico conversacional integrado aos modelos L.E.V.I., voltado à pesquisa jurídica, análise de autos, geração de minutas, resumo de documentos e consulta a pareceres; a Consulta de Pareceres por IA, destinada à pesquisa inteligente no acervo de pareceres, com busca generativa, semântica e por filtros; o Raio-X, que realiza a extração automática de dados estruturados e informações-chave de demandas judiciais para triagem inicial; o Resumo de Documentos, voltado à síntese de sentenças, acórdãos e documentos jurídicos, com estruturação de metadados, fundamentos e dispositivo; e o Relatório do Processo, que consolida múltiplos documentos dos autos em visão cronológica e estruturada do caso. Há, ainda, iniciativas correlatas em diferentes estágios de uso ou consolidação, como classificação de êxito de sentenças, integração com o PGE Digital e análise de prestações de contas, todas desenvolvidas internamente e orientadas à redução de tarefas operacionais, ao aumento da qualidade da informação e à liberação de tempo técnico para a atuação jurídica estratégica.</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>PGE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>A PGE-RJ possui solução própria de inteligência artificial, desenvolvida por servidores da Gerência de Tecnologia da Informação para uso de toda à Procuradoria.  As soluções estão sustentadas em infraestrutura própria, com destaque para o projeto L.E.V.I., voltado à aplicação de Machine Learning na automação de tarefas repetitivas, especialmente em demandas de massa, na classificação de processos administrativos e judiciais, na predição de temas e teses e no apoio à proposição automatizada de respostas às demandas apresentadas. A partir dessa base institucional, a PGE-RJ/GTI desenvolveu internamente soluções, como o LEVI Chat, assistente jurídico conversacional integrado aos modelos L.E.V.I., voltado à pesquisa jurídica, análise de autos, geração de minutas, resumo de documentos e consulta a pareceres; a Consulta de Pareceres por IA, destinada à pesquisa inteligente no acervo de pareceres, com busca generativa, semântica e por filtros; o Raio-X, que realiza a extração automática de dados estruturados e informações-chave de demandas judiciais para triagem inicial; o Resumo de Documentos, voltado à síntese de sentenças, acórdãos e documentos jurídicos, com estruturação de metadados, fundamentos e dispositivo; e o Relatório do Processo, que consolida múltiplos documentos dos autos em visão cronológica e estruturada do caso. Há, ainda, iniciativas correlatas em diferentes estágios de uso ou consolidação, como classificação de êxito de sentenças, integração com o PGE Digital e análise de prestações de contas, todas desenvolvidas internamente e orientadas à redução de tarefas operacionais, ao aumento da qualidade da informação e à liberação de tempo técnico para a atuação jurídica estratégica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>PRODERJ</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>No momento, estão sendo desenvolvidos os seguintes sistemas com uso de IA na ferramenta adquirida da IBM (Watsonx.ai Studio e Orchestrate):
 1 – Contratada IA:
@@ -4628,43 +7213,43 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>QUEIMADOS</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>O Município possui atualmente utilização institucional de soluções baseadas em Inteligência Artificial, especialmente por meio de plataformas de atendimento automatizado e automação de processos administrativos.
 O principal uso identificado ocorre através do Chatbot institucional utilizado em canais oficiais de atendimento digital, incluindo WhatsApp e Telegram, destinado ao suporte ao cidadão, disponibilização automatizada de informações, encaminhamento de solicitações e apoio à comunicação institucional.
@@ -4674,85 +7259,85 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>RIO DAS OSTRAS</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Adota em menor parte.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>A organização utiliza inteligência artificial de forma básica, gratuita e pontual, como apoio às atividades diárias e à resolução de problemas operacionais, por meio de ferramentas disponibilizadas por terceiros.</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>RIO DAS OSTRAS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>A organização utiliza inteligência artificial de forma básica, gratuita e pontual, como apoio às atividades diárias e à resolução de problemas operacionais, por meio de ferramentas disponibilizadas por terceiros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>SEAP</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>A SEPPEN/RJ não possui, até o momento, solução institucional centralizada de inteligência artificial disponibilizada oficialmente pela Administração, pela área de TI ou por outro setor para uso corporativo.
 Os usos eventualmente existentes ocorrem de forma individual e descentralizada, por iniciativa própria dos servidores ou colaboradores, mediante contas pessoais e custeio próprio, sem fornecimento, padronização, gestão contratual ou controle institucional pela SEPPEN/RJ.
@@ -4777,85 +7362,85 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SECID</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Adota em menor parte.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Adota em menor parte.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Adota em menor parte.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Não adota</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Não adota</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>SECTI</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>SISTEMAS COM IA DESENVOLVIDOS PELA SECTI-RJ
 O ATENDE.AI  é a plataforma de helpdesk de TI da SECTI-RJ, que combina um assistente virtual inteligente (Jones) com um sistema completo de gestão de chamados. Desenvolvido para atender professores, alunos e servidores de universidades e escolas técnicas do estado, o sistema prioriza a resolução ágil de problemas via IA enquanto mantém um fluxo robusto de triagem e acompanhamento de tickets. Sua interface segue rigorosamente os padrões visuais do Gov.br, garantindo acessibilidade, usabilidade e conformidade com as diretrizes de governo digital. A plataforma integra reconhecimento de voz em português brasileiro, permitindo interação inclusiva e natural com o usuário. Disponível em https://atende.secti.rj.gov.br
@@ -4879,85 +7464,85 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SEDEICS</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Adota em menor parte.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Adota em menor parte.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>SEDEICS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>SEFAZ</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>A Secretaria de Estado de Fazenda do Rio de Janeiro (SEFAZ-RJ) implementou, em seus portais 
 de serviços tributários, uma solução de atendimento digital baseada em chatbot com o objetivo de 
@@ -5004,57 +7589,20 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SEPLAG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SES</t>
+          <t>SEPLAG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adota em maior parte ou totalmente.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Adota em maior parte ou totalmente.</t>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5069,71 +7617,66 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Adota parcialmente.</t>
+          <t>Não adota.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SETD</t>
+          <t>SES</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>Adota parcialmente.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Adota em maior parte ou totalmente.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Adota parcialmente.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>A SUBEDD/SETD está desenvolvendo duas aplicações de assistente virtual que utilizam IA (tipo LLM, código aberto) para facilitar a experiência do usuário no portal RJ Digital e no sistema Radar RJ. A aplicação é desenvolvida internamente, por servidores públicos, utilizando-se a Plataforma contratada e disponibilizada pelo PRODERJ (Plataforma IBM Watson) para hospedagem e apoio ao desenvolvimento.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SETRAB</t>
+          <t>SETD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adota em menor parte.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5153,19 +7696,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Não existe adoção formal. E a curto prazo não existe plano para contratação.</t>
+          <t>A SUBEDD/SETD está desenvolvendo duas aplicações de assistente virtual que utilizam IA (tipo LLM, código aberto) para facilitar a experiência do usuário no portal RJ Digital e no sistema Radar RJ. A aplicação é desenvolvida internamente, por servidores públicos, utilizando-se a Plataforma contratada e disponibilizada pelo PRODERJ (Plataforma IBM Watson) para hospedagem e apoio ao desenvolvimento.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO</t>
+          <t>SETRAB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5200,47 +7743,89 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>No momento adquirimos Hardware e estamos em faze de teste para utilizaçao de LLM em nosso datacenter</t>
+          <t>Não existe adoção formal. E a curto prazo não existe plano para contratação.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>SÃO GONÇALO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Adota em menor parte.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>No momento adquirimos Hardware e estamos em faze de teste para utilizaçao de LLM em nosso datacenter</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>SÃO PEDRO DA ALDEIA</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>As soluções de inteligência artificial utilizadas pelo Município não são desenvolvidas internamente, sendo disponibilizadas por meio de contratos firmados com empresas especializadas que detêm essa tecnologia. São elas:
 A) Sistema Alice: na prefeitura de São Pedro da Aldeia, a ferramenta possui uma função estratégica de compliance, integridade, controle interno e governança pública; 
@@ -5249,43 +7834,43 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>TCE-RJ</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>A organização estruturou o uso de inteligência artificial por meio de um plano estratégico institucional, com iniciativas que abrangem produtividade individual,
 apoio à atividade finalística e transformação digital dos processos.
@@ -5321,43 +7906,43 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>TERESÓPOLIS</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Em atenção ao questionamento apresentado acerca da utilização de soluções de Inteligência Artificial no âmbito da Administração Municipal, cumpre informar que o Município de Teresópolis encontra-se atualmente em processo de modernização tecnológica, estruturado a partir da readequação da infraestrutura de rede, da unificação sistêmica dos ambientes administrativos e da implantação gradual de mecanismos de governança digital.
 Neste contexto, as ações atualmente desenvolvidas possuem caráter preparatório e estruturante para futura adoção ampliada de ferramentas de Inteligência Artificial, especialmente voltadas à melhoria da gestão pública, otimização de processos administrativos, ampliação da transparência, fortalecimento da segurança da informação e aprimoramento dos serviços prestados ao cidadão.
@@ -5376,43 +7961,43 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>TJRJ</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>ASSIS	Assistente para construção de minutas e responde perguntas sobre o processo.	ASSIA-SGTEC	Produção	Interno	Contratação Fábrica de Software de IA (SPASSU)
 JurisFlow	Extrator de dados estruturados de um documento jurídico.	ASSIA-SGTEC	Homologação	Interno	Contratação Fábrica de Software de IA (SPASSU)
@@ -5438,7 +8023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5486,7 +8071,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GSI</t>
+          <t>CEDAE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5501,17 +8086,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5521,29 +8106,29 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nada a declarar.</t>
+          <t>A soluções existentes -  Google Gemini (vinculado ao Google WorkSpace) e Microsoft Copilot - são utilizadas para suporte às atividades administrativas pelos funcionários da CEDAE.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IOERJ</t>
+          <t>CGE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5553,44 +8138,44 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Resposta: Não há utilização de Interligência Artificial contratada por esta organização, bem como, não há, por ora, perspectiva de contratação deste serviço e/ou similar.</t>
+          <t>A organização faz uso da IA ANIA que ajuda nos processos SEI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JAPERI</t>
+          <t>DPGE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota parcialmente.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5600,29 +8185,29 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AUXILIO EM PESQUISAS DO USUÁRIO DE ACESSO À DOCUMENTOS DE GUIA DE IPTU E DÍVIDA ATIVA</t>
+          <t>Interações básicas para elucidação de temas técnicos das áreas de negócio; automações simples para facilitação de fluxos de trabalho.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JUCERJA</t>
+          <t>GSI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adota parcialmente.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Adota em maior parte ou totalmente.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5642,52 +8227,178 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Adota em maior parte ou totalmente.</t>
+          <t>Não adota.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>O recurso de Inteligência Artificial é utilizado pela área finalística com p intuito de agilizar o procedimento de análise de julgamento  do processo de registro mercantil. O Setor responsável pelo projeto é a Secretaria Geral e a unidade usuário é a Superintendência de Registro e Comércio.</t>
+          <t>Nada a declarar.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>IOERJ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Resposta: Não há utilização de Interligência Artificial contratada por esta organização, bem como, não há, por ora, perspectiva de contratação deste serviço e/ou similar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>JAPERI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AUXILIO EM PESQUISAS DO USUÁRIO DE ACESSO À DOCUMENTOS DE GUIA DE IPTU E DÍVIDA ATIVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>JUCERJA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Adota parcialmente.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>O recurso de Inteligência Artificial é utilizado pela área finalística com p intuito de agilizar o procedimento de análise de julgamento  do processo de registro mercantil. O Setor responsável pelo projeto é a Secretaria Geral e a unidade usuário é a Superintendência de Registro e Comércio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>MARICÁ</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Justificativa apresentada pela Órgão Contratante:
 A presente contratação justifica-se pela necessidade da Administração Pública de Maricá em dispor de uma ferramenta digital que auxilie na automação de processos e na manipulação segura de dados sensíveis, a fim de garantir que as atividades administrativas sejam executadas com maior rapidez, precisão e segurança, em conformidade com os princípios da eficiência e economicidade previstos na Lei 14.133/2021.
@@ -5698,86 +8409,86 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>MESQUITA</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>A principal utilização de inteligência artificial é no Centro de Controle Operacional (CCO). Uma das funções da IA é na identificação de placas dos veículos identificados pelas câmeras.
 https://tecnologia.mesquita.rj.gov.br/?p=194</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>MPERJ</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Resposta:
 Os principais usos de inteligência artificial atualmente existentes no MPRJ estão voltados ao apoio
@@ -5831,43 +8542,43 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>NITERÓI</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>3006. Principais Usos de Inteligência Artificial na Organização
 Descreva os principais usos de inteligência artificial existentes na organização, indicando, quando possível, a finalidade, a área responsável, o estágio de utilização e se a solução é desenvolvida internamente, contratada ou disponibilizada por terceiro.
@@ -5972,43 +8683,43 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>PRODERJ</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>No momento, estão sendo desenvolvidos os seguintes sistemas com uso de IA na ferramenta adquirida da IBM (Watsonx.ai Studio e Orchestrate):
 1 – Contratada IA:
@@ -6029,43 +8740,43 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>QUEIMADOS</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>O Município possui atualmente utilização institucional de soluções baseadas em Inteligência Artificial, especialmente por meio de plataformas de atendimento automatizado e automação de processos administrativos.
 O principal uso identificado ocorre através do Chatbot institucional utilizado em canais oficiais de atendimento digital, incluindo WhatsApp e Telegram, destinado ao suporte ao cidadão, disponibilização automatizada de informações, encaminhamento de solicitações e apoio à comunicação institucional.
@@ -6075,43 +8786,43 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>SEAP</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>A SEPPEN/RJ não possui, até o momento, solução institucional centralizada de inteligência artificial disponibilizada oficialmente pela Administração, pela área de TI ou por outro setor para uso corporativo.
 Os usos eventualmente existentes ocorrem de forma individual e descentralizada, por iniciativa própria dos servidores ou colaboradores, mediante contas pessoais e custeio próprio, sem fornecimento, padronização, gestão contratual ou controle institucional pela SEPPEN/RJ.
@@ -6136,43 +8847,43 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>SEFAZ</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>A Secretaria de Estado de Fazenda do Rio de Janeiro (SEFAZ-RJ) implementou, em seus portais 
 de serviços tributários, uma solução de atendimento digital baseada em chatbot com o objetivo de 
@@ -6219,117 +8930,117 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>SEPLAG</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>SES</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>SÃO PEDRO DA ALDEIA</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>As soluções de inteligência artificial utilizadas pelo Município não são desenvolvidas internamente, sendo disponibilizadas por meio de contratos firmados com empresas especializadas que detêm essa tecnologia. São elas:
 A) Sistema Alice: na prefeitura de São Pedro da Aldeia, a ferramenta possui uma função estratégica de compliance, integridade, controle interno e governança pública; 
@@ -6338,43 +9049,43 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>TCE-RJ</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>A organização estruturou o uso de inteligência artificial por meio de um plano estratégico institucional, com iniciativas que abrangem produtividade individual,
 apoio à atividade finalística e transformação digital dos processos.
@@ -6410,43 +9121,43 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>TERESÓPOLIS</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Adota em menor parte.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Há decisão formal ou plano aprovado para adotá-lo.</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Em atenção ao questionamento apresentado acerca da utilização de soluções de Inteligência Artificial no âmbito da Administração Municipal, cumpre informar que o Município de Teresópolis encontra-se atualmente em processo de modernização tecnológica, estruturado a partir da readequação da infraestrutura de rede, da unificação sistêmica dos ambientes administrativos e da implantação gradual de mecanismos de governança digital.
 Neste contexto, as ações atualmente desenvolvidas possuem caráter preparatório e estruturante para futura adoção ampliada de ferramentas de Inteligência Artificial, especialmente voltadas à melhoria da gestão pública, otimização de processos administrativos, ampliação da transparência, fortalecimento da segurança da informação e aprimoramento dos serviços prestados ao cidadão.
@@ -6465,43 +9176,43 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>TJRJ</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Adota parcialmente.</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>ASSIS	Assistente para construção de minutas e responde perguntas sobre o processo.	ASSIA-SGTEC	Produção	Interno	Contratação Fábrica de Software de IA (SPASSU)
 JurisFlow	Extrator de dados estruturados de um documento jurídico.	ASSIA-SGTEC	Homologação	Interno	Contratação Fábrica de Software de IA (SPASSU)
@@ -6516,43 +9227,43 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>UERJ</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Não adota.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>A UERJ utiliza, em caráter experimental, a solução SollAI, ferramenta de inteligência artificial 
 generativa especializada em licitações, contratos e gestão pública. A solução tem por finalidade o apoio a processos licitatórios, 
@@ -6563,48 +9274,6 @@
 aquisição foi realizada pela Diretoria de Administração Financeira, à qual também se vincula a sua 
 utilização. Não há, no momento, outras soluções de IA contratadas pela organização nem soluções 
 desenvolvidas internamente em uso oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CEDAE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Não adota.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>A soluções existentes -  Google Gemini (vinculado ao Google WorkSpace) e Microsoft Copilot - são utilizadas para suporte às atividades administrativas pelos funcionários da CEDAE.</t>
         </is>
       </c>
     </row>
@@ -6756,7 +9425,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6776,7 +9445,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6813,7 +9482,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -9934,7 +12603,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Não adota.</t>
+          <t>Adota em maior parte ou totalmente.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
